--- a/docentes/Ángel Martínez Noe Cristobal - Estadisticos 20211.xlsx
+++ b/docentes/Ángel Martínez Noe Cristobal - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="38">
   <si>
     <t>Mat</t>
   </si>
@@ -79,37 +79,58 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>LEYVA</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>QUIAHUA</t>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
   </si>
   <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
+    <t>VANELY JUDITH</t>
+  </si>
+  <si>
+    <t>ALEXA</t>
+  </si>
+  <si>
+    <t>ARIADNA</t>
+  </si>
+  <si>
+    <t>FERNANDA</t>
+  </si>
+  <si>
+    <t>JENIFER</t>
+  </si>
+  <si>
+    <t>ELIAN</t>
+  </si>
+  <si>
     <t>DULCE MARIA</t>
-  </si>
-  <si>
-    <t>JENNIFER</t>
-  </si>
-  <si>
-    <t>ROSARIO</t>
-  </si>
-  <si>
-    <t>ELIAN</t>
   </si>
 </sst>
 </file>
@@ -536,10 +557,10 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3">
         <v>22</v>
@@ -562,10 +583,10 @@
         <v>34</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>1</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>33</v>
@@ -574,7 +595,7 @@
         <v>97.06</v>
       </c>
       <c r="H4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -627,16 +648,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>74.36</v>
+      </c>
+      <c r="H2">
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -650,16 +674,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>57.14</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -673,16 +700,19 @@
         <v>34</v>
       </c>
       <c r="D4">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
         <v>33</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>97.06</v>
+      </c>
+      <c r="H4">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -738,13 +768,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>84.62</v>
+        <v>74.36</v>
       </c>
       <c r="H2">
         <v>7.2</v>
@@ -761,19 +791,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>62.86</v>
+        <v>60</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -787,10 +817,10 @@
         <v>34</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>1</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>33</v>
@@ -799,7 +829,7 @@
         <v>97.06</v>
       </c>
       <c r="H4">
-        <v>9.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -809,7 +839,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -841,94 +871,163 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920311</v>
+        <v>20330051920220</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920223</v>
+        <v>20330051920296</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920253</v>
+        <v>20330051920297</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920298</v>
+        <v>20330051920224</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920375</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920298</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920311</v>
+      </c>
+      <c r="B8" t="s">
         <v>26</v>
       </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="C8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" t="s">
         <v>9</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F8" t="s">
         <v>12</v>
       </c>
-      <c r="G5">
-        <v>6</v>
+      <c r="G8">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Ángel Martínez Noe Cristobal - Estadisticos 20211.xlsx
+++ b/docentes/Ángel Martínez Noe Cristobal - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="41">
   <si>
     <t>Mat</t>
   </si>
@@ -82,6 +82,9 @@
     <t>ARELLANO</t>
   </si>
   <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -100,6 +103,9 @@
     <t>ROJAS</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>PRADO</t>
   </si>
   <si>
@@ -113,6 +119,9 @@
   </si>
   <si>
     <t>VANELY JUDITH</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
   </si>
   <si>
     <t>ALEXA</t>
@@ -839,7 +848,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -877,10 +886,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -894,16 +903,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920296</v>
+        <v>20330051920287</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -912,21 +921,21 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920297</v>
+        <v>20330051920296</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -935,44 +944,44 @@
         <v>12</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920224</v>
+        <v>20330051920297</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920375</v>
+        <v>20330051920224</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -981,27 +990,27 @@
         <v>11</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920298</v>
+        <v>20330051920375</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1009,16 +1018,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920311</v>
+        <v>20330051920298</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -1027,7 +1036,30 @@
         <v>12</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920311</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Ángel Martínez Noe Cristobal - Estadisticos 20211.xlsx
+++ b/docentes/Ángel Martínez Noe Cristobal - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -79,67 +79,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>LEYVA</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>PRADO</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>VANELY JUDITH</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
     <t>ALEXA</t>
-  </si>
-  <si>
-    <t>ARIADNA</t>
-  </si>
-  <si>
-    <t>FERNANDA</t>
-  </si>
-  <si>
-    <t>JENIFER</t>
-  </si>
-  <si>
-    <t>ELIAN</t>
-  </si>
-  <si>
-    <t>DULCE MARIA</t>
   </si>
 </sst>
 </file>
@@ -683,19 +629,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>57.14</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -777,13 +723,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>74.36</v>
+        <v>84.62</v>
       </c>
       <c r="H2">
         <v>7.2</v>
@@ -803,16 +749,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F3">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G3">
-        <v>60</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -838,7 +784,7 @@
         <v>97.06</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
   </sheetData>
@@ -848,7 +794,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -880,185 +826,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920220</v>
+        <v>20330051920296</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="D2" t="s">
-        <v>33</v>
-      </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920287</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920296</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920297</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920224</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920375</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920298</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920311</v>
-      </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" t="s">
-        <v>40</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9">
         <v>1</v>
       </c>
     </row>
